--- a/Reporte_Asistencia_Procesado_Nuevo.xlsx
+++ b/Reporte_Asistencia_Procesado_Nuevo.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S112"/>
+  <dimension ref="A1:Y112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -501,13 +501,19 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -520,7 +526,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GZG Minerales | Período: 2026-08-17 a 2026-08-18 | Incluye Entrada, Salida, Exceso de Jornada y Horas Extras</t>
+          <t>GZG Minerales | Período: 2026-08-17 a 2026-08-18 | Incluye Entrada, Salida, Inicio H.E. y Fin H.E.</t>
         </is>
       </c>
     </row>
@@ -588,35 +594,65 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
+          <t>Fecha Inicio H.E.</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Hora Inicio H.E.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Punto Inicio H.E.</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Fecha Fin H.E.</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Hora Fin H.E.</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Punto Fin H.E.</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
           <t>Horas Trabajadas (HH:MM)</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Tardanza (HH:MM)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Exceso Jornada (HH:MM)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Horas Extras (HH:MM)</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>Método Verificación</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Tipo Registro</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Observación / Incidencias</t>
         </is>
@@ -663,41 +699,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr">
+        <is>
+          <t>Duplicado (Entrada)</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (20:15), Exceso de jornada no autorizado (77 min)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -762,35 +848,65 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
           <t>13:36</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>01:17</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="V6" s="6" t="inlineStr">
         <is>
           <t>01:17</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="X6" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:49, 20:15), Exceso de jornada no autorizado (77 min)</t>
         </is>
@@ -851,35 +967,65 @@
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
           <t>Imagen de cara</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -926,41 +1072,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="X8" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1025,35 +1217,65 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
           <t>12:49</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
         <is>
           <t>00:19</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="V9" s="6" t="inlineStr">
         <is>
           <t>00:19</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="W9" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:04)</t>
         </is>
@@ -1100,41 +1322,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="X10" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1199,35 +1467,65 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
           <t>12:26</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>00:10</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>00:10</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="Y11" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:48)</t>
         </is>
@@ -1274,41 +1572,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="X12" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>Exceso de jornada no autorizado (116 min)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1373,35 +1721,65 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
           <t>14:12</t>
         </is>
       </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
         <is>
           <t>01:56</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>01:56</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="W13" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="X13" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="Y13" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:47), Exceso de jornada no autorizado (116 min)</t>
         </is>
@@ -1448,41 +1826,83 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="X14" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1547,35 +1967,65 @@
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
           <t>00:09</t>
         </is>
       </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
         <is>
           <t>11:46</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>11:46</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="X15" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="Y15" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:46), Exceso de jornada no autorizado (706 min)</t>
         </is>
@@ -1619,44 +2069,94 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Duplicado (Entrada)</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (18:17), Exceso de jornada no autorizado (677 min)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1721,35 +2221,65 @@
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
           <t>12:46</t>
         </is>
       </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="W17" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="X17" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="Y17" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (18:17)</t>
         </is>
@@ -1796,41 +2326,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="X18" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1895,35 +2471,65 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
           <t>12:25</t>
         </is>
       </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="X19" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="Y19" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:39)</t>
         </is>
@@ -1984,35 +2590,65 @@
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="X20" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="Y20" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -2059,41 +2695,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="X21" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2158,35 +2840,65 @@
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
           <t>12:34</t>
         </is>
       </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
         <is>
           <t>00:23</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="V22" s="6" t="inlineStr">
         <is>
           <t>00:23</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="W22" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="X22" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S22" s="5" t="inlineStr">
+      <c r="Y22" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:11)</t>
         </is>
@@ -2233,41 +2945,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="X23" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S23" s="5" t="inlineStr"/>
+      <c r="Y23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -2332,35 +3090,65 @@
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
           <t>12:21</t>
         </is>
       </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>00:02</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="V24" s="6" t="inlineStr">
         <is>
           <t>00:02</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="W24" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="X24" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S24" s="5" t="inlineStr">
+      <c r="Y24" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:03)</t>
         </is>
@@ -2407,41 +3195,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>00:22</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>00:22</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="X25" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -2506,35 +3340,65 @@
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>00:22</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="V26" s="6" t="inlineStr">
         <is>
           <t>00:22</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="W26" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="X26" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr">
+      <c r="Y26" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:17)</t>
         </is>
@@ -2581,41 +3445,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="X27" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -2680,35 +3590,65 @@
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
           <t>12:31</t>
         </is>
       </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>00:15</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="V28" s="6" t="inlineStr">
         <is>
           <t>00:15</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="W28" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="X28" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S28" s="5" t="inlineStr">
+      <c r="Y28" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:12)</t>
         </is>
@@ -2755,41 +3695,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="X29" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -2854,35 +3840,65 @@
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
           <t>12:25</t>
         </is>
       </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
         <is>
           <t>00:04</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
+      <c r="V30" s="6" t="inlineStr">
         <is>
           <t>00:04</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="W30" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="X30" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S30" s="5" t="inlineStr">
+      <c r="Y30" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:40, 06:46)</t>
         </is>
@@ -2929,41 +3945,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>Duplicado (Entrada)</t>
+        </is>
+      </c>
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (20:16), Exceso de jornada no autorizado (76 min)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -3028,35 +4094,65 @@
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
           <t>13:11</t>
         </is>
       </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
         <is>
           <t>01:16</t>
         </is>
       </c>
-      <c r="P32" s="6" t="inlineStr">
+      <c r="V32" s="6" t="inlineStr">
         <is>
           <t>01:16</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="W32" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="X32" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S32" s="5" t="inlineStr">
+      <c r="Y32" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:12, 20:16), Exceso de jornada no autorizado (76 min)</t>
         </is>
@@ -3103,41 +4199,83 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="X33" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S33" s="5" t="inlineStr"/>
+      <c r="Y33" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida, Tardanza (5 min)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -3202,35 +4340,65 @@
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
           <t>00:38</t>
         </is>
       </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U34" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V34" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W34" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="X34" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="Y34" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:20), Salida anticipada (690 min)</t>
         </is>
@@ -3274,44 +4442,94 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="W35" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="X35" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S35" s="5" t="inlineStr"/>
+      <c r="Y35" s="5" t="inlineStr">
+        <is>
+          <t>Exceso de jornada no autorizado (710 min)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -3376,35 +4594,65 @@
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
           <t>12:10</t>
         </is>
       </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U36" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="V36" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="W36" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="X36" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S36" s="5" t="inlineStr"/>
+      <c r="Y36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -3447,41 +4695,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="6" t="inlineStr"/>
-      <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U37" s="6" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="V37" s="6" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="W37" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr">
+        <is>
+          <t>Duplicado (Entrada)</t>
+        </is>
+      </c>
+      <c r="Y37" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (20:16), Exceso de jornada no autorizado (78 min)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -3546,35 +4844,65 @@
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
           <t>13:39</t>
         </is>
       </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
         <is>
           <t>01:18</t>
         </is>
       </c>
-      <c r="P38" s="6" t="inlineStr">
+      <c r="V38" s="6" t="inlineStr">
         <is>
           <t>01:18</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="W38" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="X38" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S38" s="5" t="inlineStr">
+      <c r="Y38" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43, 20:16), Exceso de jornada no autorizado (78 min)</t>
         </is>
@@ -3618,44 +4946,86 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U39" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W39" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="X39" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S39" s="5" t="inlineStr"/>
+      <c r="Y39" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -3720,35 +5090,65 @@
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
           <t>12:29</t>
         </is>
       </c>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr">
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="P40" s="6" t="inlineStr">
+      <c r="V40" s="6" t="inlineStr">
         <is>
           <t>00:01</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="W40" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="X40" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S40" s="5" t="inlineStr"/>
+      <c r="Y40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -3788,44 +5188,86 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>00:41</t>
+        </is>
+      </c>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="X41" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S41" s="5" t="inlineStr"/>
+      <c r="Y41" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida, Tardanza (41 min)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -3890,35 +5332,65 @@
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="N42" s="6" t="inlineStr">
+      <c r="T42" s="6" t="inlineStr">
         <is>
           <t>00:41</t>
         </is>
       </c>
-      <c r="O42" s="6" t="inlineStr">
+      <c r="U42" s="6" t="inlineStr">
         <is>
           <t>00:06</t>
         </is>
       </c>
-      <c r="P42" s="6" t="inlineStr">
+      <c r="V42" s="6" t="inlineStr">
         <is>
           <t>00:06</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="W42" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="X42" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S42" s="5" t="inlineStr">
+      <c r="Y42" s="5" t="inlineStr">
         <is>
           <t>Tardanza (41 min)</t>
         </is>
@@ -3965,41 +5437,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" s="6" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="X43" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr">
+        <is>
+          <t>Tardanza (331 min)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -4064,35 +5586,65 @@
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
           <t>12:05</t>
         </is>
       </c>
-      <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W44" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="X44" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S44" s="5" t="inlineStr">
+      <c r="Y44" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (12:46)</t>
         </is>
@@ -4136,44 +5688,94 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="X45" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S45" s="5" t="inlineStr"/>
+      <c r="Y45" s="5" t="inlineStr">
+        <is>
+          <t>Exceso de jornada no autorizado (714 min)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -4238,35 +5840,65 @@
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
           <t>12:19</t>
         </is>
       </c>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W46" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="X46" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S46" s="5" t="inlineStr"/>
+      <c r="Y46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -4306,44 +5938,86 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W47" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="X47" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -4408,35 +6082,65 @@
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
           <t>12:28</t>
         </is>
       </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V48" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W48" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="X48" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S48" s="5" t="inlineStr"/>
+      <c r="Y48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -4476,44 +6180,86 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W49" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="X49" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S49" s="5" t="inlineStr"/>
+      <c r="Y49" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -4578,35 +6324,65 @@
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
           <t>12:28</t>
         </is>
       </c>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W50" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="X50" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S50" s="5" t="inlineStr"/>
+      <c r="Y50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -4646,44 +6422,86 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U51" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V51" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W51" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="X51" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -4748,35 +6566,65 @@
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
           <t>12:22</t>
         </is>
       </c>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V52" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W52" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="X52" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S52" s="5" t="inlineStr"/>
+      <c r="Y52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -4819,41 +6667,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="6" t="inlineStr"/>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="T53" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U53" s="6" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="V53" s="6" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="W53" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="X53" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -4918,35 +6812,65 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
           <t>12:29</t>
         </is>
       </c>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="inlineStr">
+      <c r="T54" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U54" s="6" t="inlineStr">
         <is>
           <t>00:12</t>
         </is>
       </c>
-      <c r="P54" s="6" t="inlineStr">
+      <c r="V54" s="6" t="inlineStr">
         <is>
           <t>00:12</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="W54" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="X54" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S54" s="5" t="inlineStr">
+      <c r="Y54" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:11)</t>
         </is>
@@ -4990,44 +6914,86 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
       <c r="K55" s="6" t="inlineStr"/>
       <c r="L55" s="6" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T55" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U55" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V55" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W55" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="X55" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S55" s="5" t="inlineStr"/>
+      <c r="Y55" s="5" t="inlineStr">
+        <is>
+          <t>Falta marcación de salida</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -5092,35 +7058,65 @@
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
           <t>12:23</t>
         </is>
       </c>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="inlineStr">
+      <c r="T56" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U56" s="6" t="inlineStr">
         <is>
           <t>00:02</t>
         </is>
       </c>
-      <c r="P56" s="6" t="inlineStr">
+      <c r="V56" s="6" t="inlineStr">
         <is>
           <t>00:02</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="W56" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="X56" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S56" s="5" t="inlineStr"/>
+      <c r="Y56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -5163,41 +7159,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr"/>
-      <c r="L57" s="6" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="T57" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U57" s="6" t="inlineStr">
+        <is>
+          <t>00:03</t>
+        </is>
+      </c>
+      <c r="V57" s="6" t="inlineStr">
+        <is>
+          <t>00:03</t>
+        </is>
+      </c>
+      <c r="W57" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="X57" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S57" s="5" t="inlineStr"/>
+      <c r="Y57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -5262,35 +7304,65 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
           <t>12:23</t>
         </is>
       </c>
-      <c r="N58" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="inlineStr">
+      <c r="T58" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U58" s="6" t="inlineStr">
         <is>
           <t>00:03</t>
         </is>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="V58" s="6" t="inlineStr">
         <is>
           <t>00:03</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="W58" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="X58" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S58" s="5" t="inlineStr">
+      <c r="Y58" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43)</t>
         </is>
@@ -5337,41 +7409,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr"/>
-      <c r="K59" s="6" t="inlineStr"/>
-      <c r="L59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="T59" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U59" s="6" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="V59" s="6" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="W59" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="X59" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S59" s="5" t="inlineStr"/>
+      <c r="Y59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -5436,35 +7554,65 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
           <t>12:32</t>
         </is>
       </c>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="inlineStr">
+      <c r="T60" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U60" s="6" t="inlineStr">
         <is>
           <t>00:17</t>
         </is>
       </c>
-      <c r="P60" s="6" t="inlineStr">
+      <c r="V60" s="6" t="inlineStr">
         <is>
           <t>00:17</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="W60" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="X60" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S60" s="5" t="inlineStr">
+      <c r="Y60" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:45)</t>
         </is>
@@ -5511,41 +7659,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr"/>
-      <c r="K61" s="6" t="inlineStr"/>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="T61" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U61" s="6" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="V61" s="6" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="W61" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="S61" s="5" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr">
+        <is>
+          <t>Duplicado (Entrada)</t>
+        </is>
+      </c>
+      <c r="Y61" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (06:36, 06:37)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -5610,35 +7808,65 @@
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
           <t>12:38</t>
         </is>
       </c>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="inlineStr">
+      <c r="T62" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U62" s="6" t="inlineStr">
         <is>
           <t>00:13</t>
         </is>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="V62" s="6" t="inlineStr">
         <is>
           <t>00:13</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="W62" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="X62" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S62" s="5" t="inlineStr">
+      <c r="Y62" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:36, 06:37, 06:38)</t>
         </is>
@@ -5685,41 +7913,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="6" t="inlineStr"/>
-      <c r="L63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="T63" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U63" s="6" t="inlineStr">
+        <is>
+          <t>00:11</t>
+        </is>
+      </c>
+      <c r="V63" s="6" t="inlineStr">
+        <is>
+          <t>00:11</t>
+        </is>
+      </c>
+      <c r="W63" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="X63" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S63" s="5" t="inlineStr"/>
+      <c r="Y63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -5784,35 +8058,65 @@
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
           <t>12:38</t>
         </is>
       </c>
-      <c r="N64" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O64" s="6" t="inlineStr">
+      <c r="T64" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U64" s="6" t="inlineStr">
         <is>
           <t>00:11</t>
         </is>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="V64" s="6" t="inlineStr">
         <is>
           <t>00:11</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
+      <c r="W64" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="X64" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="Y64" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:41)</t>
         </is>
@@ -5859,41 +8163,91 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>00:39</t>
+        </is>
+      </c>
+      <c r="U65" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V65" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W65" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="X65" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S65" s="5" t="inlineStr"/>
+      <c r="Y65" s="5" t="inlineStr">
+        <is>
+          <t>Tardanza (39 min)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -5958,35 +8312,65 @@
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
           <t>11:46</t>
         </is>
       </c>
-      <c r="N66" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q66" s="6" t="inlineStr">
+      <c r="T66" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V66" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W66" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R66" s="6" t="inlineStr">
+      <c r="X66" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S66" s="5" t="inlineStr">
+      <c r="Y66" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:54)</t>
         </is>
@@ -6033,41 +8417,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
-      <c r="L67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="T67" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U67" s="6" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="V67" s="6" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="W67" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R67" s="6" t="inlineStr">
+      <c r="X67" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S67" s="5" t="inlineStr"/>
+      <c r="Y67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -6132,35 +8562,65 @@
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
           <t>12:35</t>
         </is>
       </c>
-      <c r="N68" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O68" s="6" t="inlineStr">
+      <c r="T68" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U68" s="6" t="inlineStr">
         <is>
           <t>00:17</t>
         </is>
       </c>
-      <c r="P68" s="6" t="inlineStr">
+      <c r="V68" s="6" t="inlineStr">
         <is>
           <t>00:17</t>
         </is>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
+      <c r="W68" s="6" t="inlineStr">
         <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R68" s="6" t="inlineStr">
+      <c r="X68" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S68" s="5" t="inlineStr">
+      <c r="Y68" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:47)</t>
         </is>
@@ -6207,41 +8667,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="6" t="inlineStr"/>
-      <c r="L69" s="6" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="T69" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U69" s="6" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="V69" s="6" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="W69" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R69" s="6" t="inlineStr">
+      <c r="X69" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S69" s="5" t="inlineStr"/>
+      <c r="Y69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -6306,35 +8812,65 @@
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
           <t>12:32</t>
         </is>
       </c>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O70" s="6" t="inlineStr">
+      <c r="T70" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U70" s="6" t="inlineStr">
         <is>
           <t>00:13</t>
         </is>
       </c>
-      <c r="P70" s="6" t="inlineStr">
+      <c r="V70" s="6" t="inlineStr">
         <is>
           <t>00:13</t>
         </is>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
+      <c r="W70" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="X70" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S70" s="5" t="inlineStr">
+      <c r="Y70" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:44)</t>
         </is>
@@ -6381,41 +8917,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr"/>
-      <c r="L71" s="6" t="inlineStr"/>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V71" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W71" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
+      <c r="X71" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S71" s="5" t="inlineStr"/>
+      <c r="Y71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -6480,35 +9062,65 @@
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
           <t>12:20</t>
         </is>
       </c>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
+      <c r="T72" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U72" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V72" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W72" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R72" s="6" t="inlineStr">
+      <c r="X72" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S72" s="5" t="inlineStr">
+      <c r="Y72" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43)</t>
         </is>
@@ -6555,41 +9167,87 @@
           <t>DIA</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr"/>
-      <c r="L73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="T73" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V73" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W73" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R73" s="6" t="inlineStr">
+      <c r="X73" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S73" s="5" t="inlineStr"/>
+      <c r="Y73" s="5" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -6654,35 +9312,65 @@
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
           <t>12:29</t>
         </is>
       </c>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
+      <c r="T74" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U74" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V74" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W74" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
+      <c r="X74" s="6" t="inlineStr">
         <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="S74" s="5" t="inlineStr">
+      <c r="Y74" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:46)</t>
         </is>
@@ -6726,44 +9414,94 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr"/>
-      <c r="K75" s="6" t="inlineStr"/>
-      <c r="L75" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T75" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="V75" s="6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R75" s="6" t="inlineStr">
+      <c r="X75" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S75" s="5" t="inlineStr"/>
+      <c r="Y75" s="5" t="inlineStr">
+        <is>
+          <t>Exceso de jornada no autorizado (693 min)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -6828,35 +9566,65 @@
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
           <t>12:27</t>
         </is>
       </c>
-      <c r="N76" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O76" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="P76" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="Q76" s="6" t="inlineStr">
+      <c r="T76" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U76" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V76" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W76" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R76" s="6" t="inlineStr">
+      <c r="X76" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S76" s="5" t="inlineStr"/>
+      <c r="Y76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -6896,44 +9664,94 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="6" t="inlineStr"/>
-      <c r="K77" s="6" t="inlineStr"/>
-      <c r="L77" s="6" t="inlineStr"/>
+          <t>NOCHE</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Garita Biometrico_wifi-1</t>
         </is>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T77" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R77" s="6" t="inlineStr">
+      <c r="X77" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S77" s="5" t="inlineStr"/>
+      <c r="Y77" s="5" t="inlineStr">
+        <is>
+          <t>Exceso de jornada no autorizado (697 min)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -6998,35 +9816,65 @@
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>Garita Biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Planta_biometrico_wifi-1</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
           <t>12:29</t>
         </is>
       </c>
-      <c r="N78" s="6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="O78" s="6" t="inlineStr">
+      <c r="T78" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U78" s="6" t="inlineStr">
         <is>
           <t>00:06</t>
         </is>
       </c>
-      <c r="P78" s="6" t="inlineStr">
+      <c r="V78" s="6" t="inlineStr">
         <is>
           <t>00:06</t>
         </is>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
+      <c r="W78" s="6" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="R78" s="6" t="inlineStr">
+      <c r="X78" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S78" s="5" t="inlineStr"/>
+      <c r="Y78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -7075,35 +9923,65 @@
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T79" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R79" s="6" t="inlineStr">
+      <c r="X79" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S79" s="5" t="inlineStr"/>
+      <c r="Y79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -7152,35 +10030,65 @@
       <c r="L80" s="6" t="inlineStr"/>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U80" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V80" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W80" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R80" s="6" t="inlineStr">
+      <c r="X80" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S80" s="5" t="inlineStr"/>
+      <c r="Y80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -7229,35 +10137,65 @@
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U81" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V81" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W81" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
+      <c r="X81" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S81" s="5" t="inlineStr"/>
+      <c r="Y81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -7306,35 +10244,65 @@
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q82" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U82" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V82" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr">
+      <c r="X82" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S82" s="5" t="inlineStr"/>
+      <c r="Y82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -7383,35 +10351,65 @@
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q83" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T83" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U83" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V83" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W83" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
+      <c r="X83" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S83" s="5" t="inlineStr"/>
+      <c r="Y83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -7460,35 +10458,65 @@
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T84" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U84" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V84" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W84" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R84" s="6" t="inlineStr">
+      <c r="X84" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S84" s="5" t="inlineStr"/>
+      <c r="Y84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -7537,35 +10565,65 @@
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U85" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V85" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W85" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R85" s="6" t="inlineStr">
+      <c r="X85" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S85" s="5" t="inlineStr"/>
+      <c r="Y85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -7614,35 +10672,65 @@
       <c r="L86" s="6" t="inlineStr"/>
       <c r="M86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q86" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T86" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U86" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V86" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W86" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R86" s="6" t="inlineStr">
+      <c r="X86" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S86" s="5" t="inlineStr"/>
+      <c r="Y86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -7691,35 +10779,65 @@
       <c r="L87" s="6" t="inlineStr"/>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q87" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T87" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U87" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V87" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W87" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
+      <c r="X87" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S87" s="5" t="inlineStr"/>
+      <c r="Y87" s="5" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -7768,35 +10886,65 @@
       <c r="L88" s="6" t="inlineStr"/>
       <c r="M88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q88" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T88" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U88" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V88" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W88" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="X88" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S88" s="5" t="inlineStr"/>
+      <c r="Y88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -7845,35 +10993,65 @@
       <c r="L89" s="6" t="inlineStr"/>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q89" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T89" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U89" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V89" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W89" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R89" s="6" t="inlineStr">
+      <c r="X89" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S89" s="5" t="inlineStr"/>
+      <c r="Y89" s="5" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -7922,35 +11100,65 @@
       <c r="L90" s="6" t="inlineStr"/>
       <c r="M90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q90" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S90" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T90" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U90" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V90" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W90" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R90" s="6" t="inlineStr">
+      <c r="X90" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S90" s="5" t="inlineStr"/>
+      <c r="Y90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -7999,35 +11207,65 @@
       <c r="L91" s="6" t="inlineStr"/>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q91" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S91" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T91" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U91" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V91" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W91" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
+      <c r="X91" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S91" s="5" t="inlineStr"/>
+      <c r="Y91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -8076,35 +11314,65 @@
       <c r="L92" s="6" t="inlineStr"/>
       <c r="M92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q92" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T92" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U92" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V92" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W92" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R92" s="6" t="inlineStr">
+      <c r="X92" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S92" s="5" t="inlineStr"/>
+      <c r="Y92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -8153,35 +11421,65 @@
       <c r="L93" s="6" t="inlineStr"/>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q93" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T93" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U93" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V93" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W93" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R93" s="6" t="inlineStr">
+      <c r="X93" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S93" s="5" t="inlineStr"/>
+      <c r="Y93" s="5" t="inlineStr"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -8230,35 +11528,65 @@
       <c r="L94" s="6" t="inlineStr"/>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q94" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T94" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U94" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V94" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W94" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R94" s="6" t="inlineStr">
+      <c r="X94" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S94" s="5" t="inlineStr"/>
+      <c r="Y94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -8307,35 +11635,65 @@
       <c r="L95" s="6" t="inlineStr"/>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q95" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T95" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U95" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V95" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W95" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R95" s="6" t="inlineStr">
+      <c r="X95" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S95" s="5" t="inlineStr"/>
+      <c r="Y95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -8384,35 +11742,65 @@
       <c r="L96" s="6" t="inlineStr"/>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q96" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S96" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T96" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U96" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V96" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W96" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R96" s="6" t="inlineStr">
+      <c r="X96" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S96" s="5" t="inlineStr"/>
+      <c r="Y96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -8461,35 +11849,65 @@
       <c r="L97" s="6" t="inlineStr"/>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q97" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T97" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U97" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V97" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W97" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R97" s="6" t="inlineStr">
+      <c r="X97" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S97" s="5" t="inlineStr"/>
+      <c r="Y97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -8538,35 +11956,65 @@
       <c r="L98" s="6" t="inlineStr"/>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q98" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R98" s="6" t="inlineStr">
+      <c r="X98" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S98" s="5" t="inlineStr"/>
+      <c r="Y98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -8615,35 +12063,65 @@
       <c r="L99" s="6" t="inlineStr"/>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q99" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T99" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U99" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V99" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W99" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R99" s="6" t="inlineStr">
+      <c r="X99" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S99" s="5" t="inlineStr"/>
+      <c r="Y99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -8692,35 +12170,65 @@
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q100" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S100" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T100" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U100" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V100" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W100" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R100" s="6" t="inlineStr">
+      <c r="X100" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S100" s="5" t="inlineStr"/>
+      <c r="Y100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -8769,35 +12277,65 @@
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q101" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S101" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T101" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U101" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V101" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W101" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R101" s="6" t="inlineStr">
+      <c r="X101" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S101" s="5" t="inlineStr"/>
+      <c r="Y101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -8846,35 +12384,65 @@
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q102" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S102" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T102" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U102" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V102" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W102" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R102" s="6" t="inlineStr">
+      <c r="X102" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S102" s="5" t="inlineStr"/>
+      <c r="Y102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -8923,35 +12491,65 @@
       <c r="L103" s="6" t="inlineStr"/>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q103" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S103" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T103" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U103" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V103" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W103" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R103" s="6" t="inlineStr">
+      <c r="X103" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S103" s="5" t="inlineStr"/>
+      <c r="Y103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -9000,35 +12598,65 @@
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q104" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R104" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S104" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T104" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U104" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V104" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W104" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R104" s="6" t="inlineStr">
+      <c r="X104" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S104" s="5" t="inlineStr"/>
+      <c r="Y104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -9077,35 +12705,65 @@
       <c r="L105" s="6" t="inlineStr"/>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q105" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T105" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U105" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V105" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W105" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R105" s="6" t="inlineStr">
+      <c r="X105" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S105" s="5" t="inlineStr"/>
+      <c r="Y105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -9154,35 +12812,65 @@
       <c r="L106" s="6" t="inlineStr"/>
       <c r="M106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q106" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T106" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U106" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V106" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W106" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R106" s="6" t="inlineStr">
+      <c r="X106" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S106" s="5" t="inlineStr"/>
+      <c r="Y106" s="5" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -9231,35 +12919,65 @@
       <c r="L107" s="6" t="inlineStr"/>
       <c r="M107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q107" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R107" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S107" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T107" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U107" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V107" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W107" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R107" s="6" t="inlineStr">
+      <c r="X107" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S107" s="5" t="inlineStr"/>
+      <c r="Y107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -9308,35 +13026,65 @@
       <c r="L108" s="6" t="inlineStr"/>
       <c r="M108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q108" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R108" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S108" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T108" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U108" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V108" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W108" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R108" s="6" t="inlineStr">
+      <c r="X108" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S108" s="5" t="inlineStr"/>
+      <c r="Y108" s="5" t="inlineStr"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
@@ -9385,35 +13133,65 @@
       <c r="L109" s="6" t="inlineStr"/>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q109" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R109" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S109" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T109" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U109" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V109" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W109" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R109" s="6" t="inlineStr">
+      <c r="X109" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S109" s="5" t="inlineStr"/>
+      <c r="Y109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
@@ -9462,35 +13240,65 @@
       <c r="L110" s="6" t="inlineStr"/>
       <c r="M110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q110" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R110" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S110" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T110" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U110" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V110" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W110" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R110" s="6" t="inlineStr">
+      <c r="X110" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S110" s="5" t="inlineStr"/>
+      <c r="Y110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -9539,35 +13347,65 @@
       <c r="L111" s="6" t="inlineStr"/>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q111" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R111" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S111" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T111" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U111" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V111" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W111" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R111" s="6" t="inlineStr">
+      <c r="X111" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S111" s="5" t="inlineStr"/>
+      <c r="Y111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -9616,40 +13454,70 @@
       <c r="L112" s="6" t="inlineStr"/>
       <c r="M112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q112" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R112" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S112" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="T112" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="U112" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="V112" s="6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="W112" s="6" t="inlineStr">
+        <is>
           <t>Huella dactilar</t>
         </is>
       </c>
-      <c r="R112" s="6" t="inlineStr">
+      <c r="X112" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="S112" s="5" t="inlineStr"/>
+      <c r="Y112" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:Y1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reporte_Asistencia_Procesado_Nuevo.xlsx
+++ b/Reporte_Asistencia_Procesado_Nuevo.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y112"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -503,17 +503,15 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="48" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -604,55 +602,45 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Punto Inicio H.E.</t>
+          <t>Fecha Fin H.E.</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Fecha Fin H.E.</t>
+          <t>Hora Fin H.E.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Hora Fin H.E.</t>
+          <t>Horas Trabajadas (HH:MM)</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>Punto Fin H.E.</t>
+          <t>Tardanza (HH:MM)</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>Horas Trabajadas (HH:MM)</t>
+          <t>Exceso Jornada (HH:MM)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Tardanza (HH:MM)</t>
+          <t>Horas Extras (HH:MM)</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Exceso Jornada (HH:MM)</t>
+          <t>Método Verificación</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Horas Extras (HH:MM)</t>
+          <t>Tipo Registro</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>Método Verificación</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo Registro</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Observación / Incidencias</t>
         </is>
@@ -731,55 +719,45 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>01:17</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:17</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>01:17</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (20:15), Exceso de jornada no autorizado (77 min)</t>
         </is>
@@ -858,55 +836,45 @@
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>01:17</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:17</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>01:17</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:49, 20:15), Exceso de jornada no autorizado (77 min)</t>
         </is>
@@ -987,12 +955,12 @@
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -1007,25 +975,15 @@
       </c>
       <c r="U7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Imagen de cara</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>Imagen de cara</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -1104,55 +1062,45 @@
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>00:19</t>
-        </is>
-      </c>
-      <c r="W8" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1227,55 +1175,45 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>00:19</t>
-        </is>
-      </c>
-      <c r="W9" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y9" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:04)</t>
         </is>
@@ -1354,55 +1292,45 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1477,55 +1405,45 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>00:10</t>
-        </is>
-      </c>
-      <c r="W11" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y11" s="5" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:48)</t>
         </is>
@@ -1604,55 +1522,45 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>01:56</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>01:56</t>
-        </is>
-      </c>
-      <c r="W12" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
+      <c r="W12" s="5" t="inlineStr">
         <is>
           <t>Exceso de jornada no autorizado (116 min)</t>
         </is>
@@ -1731,55 +1639,45 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:56</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>01:56</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>01:56</t>
-        </is>
-      </c>
-      <c r="W13" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y13" s="5" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:47), Exceso de jornada no autorizado (116 min)</t>
         </is>
@@ -1860,12 +1758,12 @@
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -1880,25 +1778,15 @@
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y14" s="5" t="inlineStr">
+      <c r="W14" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -1955,49 +1843,41 @@
           <t>06:37</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>06:46</t>
-        </is>
-      </c>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2007,27 +1887,17 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y15" s="5" t="inlineStr">
-        <is>
-          <t>Entrada duplicada (06:46), Exceso de jornada no autorizado (706 min)</t>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (06:46)</t>
         </is>
       </c>
     </row>
@@ -2082,49 +1952,41 @@
           <t>18:16</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -2134,27 +1996,17 @@
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="W16" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>Entrada duplicada (18:17), Exceso de jornada no autorizado (677 min)</t>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (18:17)</t>
         </is>
       </c>
     </row>
@@ -2231,55 +2083,45 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
-        </is>
-      </c>
-      <c r="W17" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="inlineStr">
+      <c r="W17" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (18:17)</t>
         </is>
@@ -2358,55 +2200,45 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
-        </is>
-      </c>
-      <c r="W18" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2481,55 +2313,45 @@
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
-        </is>
-      </c>
-      <c r="W19" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y19" s="5" t="inlineStr">
+      <c r="W19" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:39)</t>
         </is>
@@ -2610,12 +2432,12 @@
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -2630,25 +2452,15 @@
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W20" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X20" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y20" s="5" t="inlineStr">
+      <c r="W20" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -2727,55 +2539,45 @@
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>00:23</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>00:23</t>
-        </is>
-      </c>
-      <c r="W21" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X21" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2850,55 +2652,45 @@
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>00:23</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>00:23</t>
-        </is>
-      </c>
-      <c r="W22" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X22" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y22" s="5" t="inlineStr">
+      <c r="W22" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:11)</t>
         </is>
@@ -2977,55 +2769,45 @@
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
-        </is>
-      </c>
-      <c r="W23" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X23" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3100,55 +2882,45 @@
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X24" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y24" s="5" t="inlineStr">
+      <c r="W24" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:03)</t>
         </is>
@@ -3227,55 +2999,45 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>00:22</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:22</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>00:22</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>00:22</t>
-        </is>
-      </c>
-      <c r="W25" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X25" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3350,55 +3112,45 @@
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>00:22</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:22</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>00:22</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>00:22</t>
-        </is>
-      </c>
-      <c r="W26" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X26" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y26" s="5" t="inlineStr">
+      <c r="W26" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:17)</t>
         </is>
@@ -3477,55 +3229,45 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="W27" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X27" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -3600,55 +3342,45 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="W28" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X28" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y28" s="5" t="inlineStr">
+      <c r="W28" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:12)</t>
         </is>
@@ -3727,55 +3459,45 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>00:04</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:04</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>00:04</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>00:04</t>
-        </is>
-      </c>
-      <c r="W29" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X29" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -3850,55 +3572,45 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>00:04</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:04</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>00:04</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>00:04</t>
-        </is>
-      </c>
-      <c r="W30" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X30" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y30" s="5" t="inlineStr">
+      <c r="W30" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:40, 06:46)</t>
         </is>
@@ -3977,55 +3689,45 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>01:16</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y31" s="5" t="inlineStr">
+      <c r="W31" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (20:16), Exceso de jornada no autorizado (76 min)</t>
         </is>
@@ -4104,55 +3806,45 @@
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>01:16</t>
-        </is>
-      </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y32" s="5" t="inlineStr">
+      <c r="W32" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:12, 20:16), Exceso de jornada no autorizado (76 min)</t>
         </is>
@@ -4233,12 +3925,12 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
@@ -4248,30 +3940,20 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W33" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X33" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y33" s="5" t="inlineStr">
+      <c r="W33" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida, Tardanza (5 min)</t>
         </is>
@@ -4328,16 +4010,8 @@
           <t>06:41</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4360,17 +4034,17 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>00:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -4380,27 +4054,17 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W34" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X34" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y34" s="5" t="inlineStr">
-        <is>
-          <t>Entrada duplicada (07:20), Salida anticipada (690 min)</t>
+      <c r="W34" s="5" t="inlineStr">
+        <is>
+          <t>Entrada duplicada (07:20)</t>
         </is>
       </c>
     </row>
@@ -4455,44 +4119,36 @@
           <t>18:50</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
@@ -4507,29 +4163,15 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="W35" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X35" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y35" s="5" t="inlineStr">
-        <is>
-          <t>Exceso de jornada no autorizado (710 min)</t>
-        </is>
-      </c>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -4604,55 +4246,45 @@
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
-        </is>
-      </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X36" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -4727,55 +4359,45 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>01:18</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:18</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>01:18</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>01:18</t>
-        </is>
-      </c>
-      <c r="W37" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X37" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y37" s="5" t="inlineStr">
+      <c r="W37" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (20:16), Exceso de jornada no autorizado (78 min)</t>
         </is>
@@ -4854,55 +4476,45 @@
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>01:18</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:18</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>01:18</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>01:18</t>
-        </is>
-      </c>
-      <c r="W38" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X38" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y38" s="5" t="inlineStr">
+      <c r="W38" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43, 20:16), Exceso de jornada no autorizado (78 min)</t>
         </is>
@@ -4983,12 +4595,12 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -5003,25 +4615,15 @@
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W39" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X39" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y39" s="5" t="inlineStr">
+      <c r="W39" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -5100,55 +4702,45 @@
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>00:01</t>
-        </is>
-      </c>
-      <c r="W40" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X40" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y40" s="5" t="inlineStr"/>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -5225,12 +4817,12 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:41</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
@@ -5240,30 +4832,20 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W41" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X41" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y41" s="5" t="inlineStr">
+      <c r="W41" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida, Tardanza (41 min)</t>
         </is>
@@ -5342,55 +4924,45 @@
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:41</t>
         </is>
       </c>
       <c r="S42" s="6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>00:06</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>00:06</t>
-        </is>
-      </c>
-      <c r="W42" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X42" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y42" s="5" t="inlineStr">
+      <c r="W42" s="5" t="inlineStr">
         <is>
           <t>Tardanza (41 min)</t>
         </is>
@@ -5479,45 +5051,35 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>05:31</t>
         </is>
       </c>
       <c r="S43" s="6" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>05:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W43" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X43" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y43" s="5" t="inlineStr">
+      <c r="W43" s="5" t="inlineStr">
         <is>
           <t>Tardanza (331 min)</t>
         </is>
@@ -5606,17 +5168,17 @@
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S44" s="6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -5626,25 +5188,15 @@
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W44" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X44" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y44" s="5" t="inlineStr">
+      <c r="W44" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (12:46)</t>
         </is>
@@ -5688,57 +5240,49 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>NOCHE</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>18:54</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>18:54</t>
-        </is>
-      </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S45" s="6" t="inlineStr">
@@ -5753,27 +5297,17 @@
       </c>
       <c r="U45" s="6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="W45" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Y45" s="5" t="inlineStr">
-        <is>
-          <t>Exceso de jornada no autorizado (714 min)</t>
+          <t>Salida sin entrada</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr">
+        <is>
+          <t>Salida sin registro de entrada previa (18:54)</t>
         </is>
       </c>
     </row>
@@ -5860,17 +5394,17 @@
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S46" s="6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T46" s="6" t="inlineStr">
@@ -5880,25 +5414,15 @@
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W46" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X46" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y46" s="5" t="inlineStr"/>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -5975,12 +5499,12 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S47" s="6" t="inlineStr">
@@ -5995,25 +5519,15 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W47" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X47" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y47" s="5" t="inlineStr">
+      <c r="W47" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -6102,17 +5616,17 @@
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S48" s="6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -6122,25 +5636,15 @@
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W48" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X48" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y48" s="5" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -6217,12 +5721,12 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S49" s="6" t="inlineStr">
@@ -6237,25 +5741,15 @@
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W49" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X49" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y49" s="5" t="inlineStr">
+      <c r="W49" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -6344,17 +5838,17 @@
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S50" s="6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
@@ -6364,25 +5858,15 @@
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W50" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X50" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y50" s="5" t="inlineStr"/>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -6459,12 +5943,12 @@
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S51" s="6" t="inlineStr">
@@ -6479,25 +5963,15 @@
       </c>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W51" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X51" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y51" s="5" t="inlineStr">
+      <c r="W51" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -6586,17 +6060,17 @@
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S52" s="6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T52" s="6" t="inlineStr">
@@ -6606,25 +6080,15 @@
       </c>
       <c r="U52" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W52" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X52" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y52" s="5" t="inlineStr"/>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -6699,55 +6163,45 @@
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S53" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="U53" s="6" t="inlineStr">
         <is>
-          <t>00:12</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>00:12</t>
-        </is>
-      </c>
-      <c r="W53" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X53" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -6822,55 +6276,45 @@
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S54" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:12</t>
         </is>
       </c>
       <c r="U54" s="6" t="inlineStr">
         <is>
-          <t>00:12</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>00:12</t>
-        </is>
-      </c>
-      <c r="W54" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X54" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y54" s="5" t="inlineStr">
+      <c r="W54" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:11)</t>
         </is>
@@ -6951,12 +6395,12 @@
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S55" s="6" t="inlineStr">
@@ -6971,25 +6415,15 @@
       </c>
       <c r="U55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W55" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X55" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y55" s="5" t="inlineStr">
+      <c r="W55" s="5" t="inlineStr">
         <is>
           <t>Falta marcación de salida</t>
         </is>
@@ -7068,55 +6502,45 @@
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S56" s="6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>00:02</t>
-        </is>
-      </c>
-      <c r="W56" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X56" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -7191,55 +6615,45 @@
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>00:03</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:03</t>
         </is>
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
-          <t>00:03</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>00:03</t>
-        </is>
-      </c>
-      <c r="W57" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X57" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y57" s="5" t="inlineStr"/>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -7314,55 +6728,45 @@
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>00:03</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:03</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>00:03</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>00:03</t>
-        </is>
-      </c>
-      <c r="W58" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X58" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y58" s="5" t="inlineStr">
+      <c r="W58" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43)</t>
         </is>
@@ -7441,55 +6845,45 @@
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S59" s="6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="U59" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
-        </is>
-      </c>
-      <c r="W59" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X59" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y59" s="5" t="inlineStr"/>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -7564,55 +6958,45 @@
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
-        </is>
-      </c>
-      <c r="W60" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X60" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y60" s="5" t="inlineStr">
+      <c r="W60" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:45)</t>
         </is>
@@ -7691,55 +7075,45 @@
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S61" s="6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="U61" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
-        </is>
-      </c>
-      <c r="W61" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X61" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y61" s="5" t="inlineStr">
+      <c r="W61" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:36, 06:37)</t>
         </is>
@@ -7818,55 +7192,45 @@
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S62" s="6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="U62" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
-        </is>
-      </c>
-      <c r="W62" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X62" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y62" s="5" t="inlineStr">
+      <c r="W62" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:36, 06:37, 06:38)</t>
         </is>
@@ -7945,55 +7309,45 @@
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="T63" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V63" s="6" t="inlineStr">
         <is>
-          <t>00:11</t>
-        </is>
-      </c>
-      <c r="W63" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X63" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y63" s="5" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -8068,55 +7422,45 @@
       </c>
       <c r="O64" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S64" s="6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:11</t>
         </is>
       </c>
       <c r="U64" s="6" t="inlineStr">
         <is>
-          <t>00:11</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V64" s="6" t="inlineStr">
         <is>
-          <t>00:11</t>
-        </is>
-      </c>
-      <c r="W64" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X64" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y64" s="5" t="inlineStr">
+      <c r="W64" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:41)</t>
         </is>
@@ -8205,45 +7549,35 @@
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:39</t>
         </is>
       </c>
       <c r="S65" s="6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
         <is>
-          <t>00:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V65" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W65" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X65" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y65" s="5" t="inlineStr">
+      <c r="W65" s="5" t="inlineStr">
         <is>
           <t>Tardanza (39 min)</t>
         </is>
@@ -8332,17 +7666,17 @@
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S66" s="6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
@@ -8352,25 +7686,15 @@
       </c>
       <c r="U66" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V66" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W66" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X66" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y66" s="5" t="inlineStr">
+      <c r="W66" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (07:54)</t>
         </is>
@@ -8449,55 +7773,45 @@
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S67" s="6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V67" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
-        </is>
-      </c>
-      <c r="W67" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X67" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y67" s="5" t="inlineStr"/>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -8572,55 +7886,45 @@
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S68" s="6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V68" s="6" t="inlineStr">
         <is>
-          <t>00:17</t>
-        </is>
-      </c>
-      <c r="W68" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X68" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y68" s="5" t="inlineStr">
+      <c r="W68" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:47)</t>
         </is>
@@ -8699,55 +8003,45 @@
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S69" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="U69" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V69" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
-        </is>
-      </c>
-      <c r="W69" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X69" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y69" s="5" t="inlineStr"/>
+      <c r="W69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -8822,55 +8116,45 @@
       </c>
       <c r="O70" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S70" s="6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:13</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V70" s="6" t="inlineStr">
         <is>
-          <t>00:13</t>
-        </is>
-      </c>
-      <c r="W70" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X70" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y70" s="5" t="inlineStr">
+      <c r="W70" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:44)</t>
         </is>
@@ -8959,17 +8243,17 @@
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -8979,25 +8263,15 @@
       </c>
       <c r="U71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V71" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W71" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X71" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y71" s="5" t="inlineStr"/>
+      <c r="W71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -9082,17 +8356,17 @@
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -9102,25 +8376,15 @@
       </c>
       <c r="U72" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V72" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W72" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X72" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y72" s="5" t="inlineStr">
+      <c r="W72" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:43)</t>
         </is>
@@ -9209,17 +8473,17 @@
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S73" s="6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -9229,25 +8493,15 @@
       </c>
       <c r="U73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V73" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W73" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X73" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y73" s="5" t="inlineStr"/>
+      <c r="W73" s="5" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -9332,17 +8586,17 @@
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S74" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -9352,25 +8606,15 @@
       </c>
       <c r="U74" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V74" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W74" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X74" s="6" t="inlineStr">
-        <is>
           <t>Duplicado (Entrada)</t>
         </is>
       </c>
-      <c r="Y74" s="5" t="inlineStr">
+      <c r="W74" s="5" t="inlineStr">
         <is>
           <t>Entrada duplicada (06:46)</t>
         </is>
@@ -9427,44 +8671,36 @@
           <t>18:33</t>
         </is>
       </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
+      <c r="K75" s="6" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S75" s="6" t="inlineStr">
@@ -9479,29 +8715,15 @@
       </c>
       <c r="U75" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V75" s="6" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="W75" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X75" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y75" s="5" t="inlineStr">
-        <is>
-          <t>Exceso de jornada no autorizado (693 min)</t>
-        </is>
-      </c>
+      <c r="W75" s="5" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -9586,17 +8808,17 @@
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S76" s="6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T76" s="6" t="inlineStr">
@@ -9606,25 +8828,15 @@
       </c>
       <c r="U76" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V76" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W76" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X76" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y76" s="5" t="inlineStr"/>
+      <c r="W76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -9677,44 +8889,36 @@
           <t>18:37</t>
         </is>
       </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="L77" s="6" t="inlineStr">
-        <is>
-          <t>18:37</t>
-        </is>
-      </c>
+      <c r="K77" s="6" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S77" s="6" t="inlineStr">
@@ -9729,29 +8933,15 @@
       </c>
       <c r="U77" s="6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V77" s="6" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="W77" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X77" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y77" s="5" t="inlineStr">
-        <is>
-          <t>Exceso de jornada no autorizado (697 min)</t>
-        </is>
-      </c>
+      <c r="W77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -9826,55 +9016,45 @@
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>Garita Biometrico_wifi-1</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>Planta_biometrico_wifi-1</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S78" s="6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:06</t>
         </is>
       </c>
       <c r="U78" s="6" t="inlineStr">
         <is>
-          <t>00:06</t>
+          <t>Tarjeta</t>
         </is>
       </c>
       <c r="V78" s="6" t="inlineStr">
         <is>
-          <t>00:06</t>
-        </is>
-      </c>
-      <c r="W78" s="6" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="X78" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y78" s="5" t="inlineStr"/>
+      <c r="W78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -9943,12 +9123,12 @@
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S79" s="6" t="inlineStr">
@@ -9963,25 +9143,15 @@
       </c>
       <c r="U79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V79" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W79" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X79" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y79" s="5" t="inlineStr"/>
+      <c r="W79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -10050,12 +9220,12 @@
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S80" s="6" t="inlineStr">
@@ -10070,25 +9240,15 @@
       </c>
       <c r="U80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V80" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W80" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X80" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y80" s="5" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -10157,12 +9317,12 @@
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S81" s="6" t="inlineStr">
@@ -10177,25 +9337,15 @@
       </c>
       <c r="U81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V81" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W81" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X81" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y81" s="5" t="inlineStr"/>
+      <c r="W81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -10264,12 +9414,12 @@
       </c>
       <c r="Q82" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S82" s="6" t="inlineStr">
@@ -10284,25 +9434,15 @@
       </c>
       <c r="U82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V82" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X82" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y82" s="5" t="inlineStr"/>
+      <c r="W82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -10371,12 +9511,12 @@
       </c>
       <c r="Q83" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S83" s="6" t="inlineStr">
@@ -10391,25 +9531,15 @@
       </c>
       <c r="U83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V83" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W83" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X83" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y83" s="5" t="inlineStr"/>
+      <c r="W83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -10478,12 +9608,12 @@
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S84" s="6" t="inlineStr">
@@ -10498,25 +9628,15 @@
       </c>
       <c r="U84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V84" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W84" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X84" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y84" s="5" t="inlineStr"/>
+      <c r="W84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -10585,12 +9705,12 @@
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S85" s="6" t="inlineStr">
@@ -10605,25 +9725,15 @@
       </c>
       <c r="U85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V85" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W85" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X85" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y85" s="5" t="inlineStr"/>
+      <c r="W85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -10692,12 +9802,12 @@
       </c>
       <c r="Q86" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S86" s="6" t="inlineStr">
@@ -10712,25 +9822,15 @@
       </c>
       <c r="U86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V86" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W86" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X86" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y86" s="5" t="inlineStr"/>
+      <c r="W86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -10799,12 +9899,12 @@
       </c>
       <c r="Q87" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S87" s="6" t="inlineStr">
@@ -10819,25 +9919,15 @@
       </c>
       <c r="U87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V87" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W87" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X87" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y87" s="5" t="inlineStr"/>
+      <c r="W87" s="5" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -10906,12 +9996,12 @@
       </c>
       <c r="Q88" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S88" s="6" t="inlineStr">
@@ -10926,25 +10016,15 @@
       </c>
       <c r="U88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V88" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W88" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X88" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y88" s="5" t="inlineStr"/>
+      <c r="W88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -11013,12 +10093,12 @@
       </c>
       <c r="Q89" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S89" s="6" t="inlineStr">
@@ -11033,25 +10113,15 @@
       </c>
       <c r="U89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V89" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W89" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X89" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y89" s="5" t="inlineStr"/>
+      <c r="W89" s="5" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -11120,12 +10190,12 @@
       </c>
       <c r="Q90" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S90" s="6" t="inlineStr">
@@ -11140,25 +10210,15 @@
       </c>
       <c r="U90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V90" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W90" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X90" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y90" s="5" t="inlineStr"/>
+      <c r="W90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -11227,12 +10287,12 @@
       </c>
       <c r="Q91" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S91" s="6" t="inlineStr">
@@ -11247,25 +10307,15 @@
       </c>
       <c r="U91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V91" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W91" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X91" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y91" s="5" t="inlineStr"/>
+      <c r="W91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -11334,12 +10384,12 @@
       </c>
       <c r="Q92" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S92" s="6" t="inlineStr">
@@ -11354,25 +10404,15 @@
       </c>
       <c r="U92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V92" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W92" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X92" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y92" s="5" t="inlineStr"/>
+      <c r="W92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -11441,12 +10481,12 @@
       </c>
       <c r="Q93" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S93" s="6" t="inlineStr">
@@ -11461,25 +10501,15 @@
       </c>
       <c r="U93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V93" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W93" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X93" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y93" s="5" t="inlineStr"/>
+      <c r="W93" s="5" t="inlineStr"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -11548,12 +10578,12 @@
       </c>
       <c r="Q94" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S94" s="6" t="inlineStr">
@@ -11568,25 +10598,15 @@
       </c>
       <c r="U94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V94" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W94" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X94" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y94" s="5" t="inlineStr"/>
+      <c r="W94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -11655,12 +10675,12 @@
       </c>
       <c r="Q95" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S95" s="6" t="inlineStr">
@@ -11675,25 +10695,15 @@
       </c>
       <c r="U95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V95" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W95" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X95" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y95" s="5" t="inlineStr"/>
+      <c r="W95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -11762,12 +10772,12 @@
       </c>
       <c r="Q96" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S96" s="6" t="inlineStr">
@@ -11782,25 +10792,15 @@
       </c>
       <c r="U96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V96" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W96" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X96" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y96" s="5" t="inlineStr"/>
+      <c r="W96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -11869,12 +10869,12 @@
       </c>
       <c r="Q97" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S97" s="6" t="inlineStr">
@@ -11889,25 +10889,15 @@
       </c>
       <c r="U97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V97" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W97" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X97" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y97" s="5" t="inlineStr"/>
+      <c r="W97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -11976,12 +10966,12 @@
       </c>
       <c r="Q98" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S98" s="6" t="inlineStr">
@@ -11996,25 +10986,15 @@
       </c>
       <c r="U98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V98" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W98" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X98" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y98" s="5" t="inlineStr"/>
+      <c r="W98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -12083,12 +11063,12 @@
       </c>
       <c r="Q99" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S99" s="6" t="inlineStr">
@@ -12103,25 +11083,15 @@
       </c>
       <c r="U99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V99" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W99" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X99" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y99" s="5" t="inlineStr"/>
+      <c r="W99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -12190,12 +11160,12 @@
       </c>
       <c r="Q100" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S100" s="6" t="inlineStr">
@@ -12210,25 +11180,15 @@
       </c>
       <c r="U100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V100" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W100" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X100" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y100" s="5" t="inlineStr"/>
+      <c r="W100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -12297,12 +11257,12 @@
       </c>
       <c r="Q101" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S101" s="6" t="inlineStr">
@@ -12317,25 +11277,15 @@
       </c>
       <c r="U101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V101" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W101" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X101" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y101" s="5" t="inlineStr"/>
+      <c r="W101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -12404,12 +11354,12 @@
       </c>
       <c r="Q102" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R102" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S102" s="6" t="inlineStr">
@@ -12424,25 +11374,15 @@
       </c>
       <c r="U102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V102" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W102" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X102" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y102" s="5" t="inlineStr"/>
+      <c r="W102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -12511,12 +11451,12 @@
       </c>
       <c r="Q103" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R103" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S103" s="6" t="inlineStr">
@@ -12531,25 +11471,15 @@
       </c>
       <c r="U103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V103" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W103" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X103" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y103" s="5" t="inlineStr"/>
+      <c r="W103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -12618,12 +11548,12 @@
       </c>
       <c r="Q104" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R104" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S104" s="6" t="inlineStr">
@@ -12638,25 +11568,15 @@
       </c>
       <c r="U104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V104" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W104" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X104" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y104" s="5" t="inlineStr"/>
+      <c r="W104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -12725,12 +11645,12 @@
       </c>
       <c r="Q105" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R105" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S105" s="6" t="inlineStr">
@@ -12745,25 +11665,15 @@
       </c>
       <c r="U105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V105" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W105" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X105" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y105" s="5" t="inlineStr"/>
+      <c r="W105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -12832,12 +11742,12 @@
       </c>
       <c r="Q106" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R106" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S106" s="6" t="inlineStr">
@@ -12852,25 +11762,15 @@
       </c>
       <c r="U106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V106" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W106" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X106" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y106" s="5" t="inlineStr"/>
+      <c r="W106" s="5" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -12939,12 +11839,12 @@
       </c>
       <c r="Q107" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R107" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S107" s="6" t="inlineStr">
@@ -12959,25 +11859,15 @@
       </c>
       <c r="U107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V107" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W107" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X107" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y107" s="5" t="inlineStr"/>
+      <c r="W107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -13046,12 +11936,12 @@
       </c>
       <c r="Q108" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R108" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S108" s="6" t="inlineStr">
@@ -13066,25 +11956,15 @@
       </c>
       <c r="U108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V108" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W108" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X108" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y108" s="5" t="inlineStr"/>
+      <c r="W108" s="5" t="inlineStr"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
@@ -13153,12 +12033,12 @@
       </c>
       <c r="Q109" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R109" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S109" s="6" t="inlineStr">
@@ -13173,25 +12053,15 @@
       </c>
       <c r="U109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V109" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W109" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X109" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y109" s="5" t="inlineStr"/>
+      <c r="W109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
@@ -13260,12 +12130,12 @@
       </c>
       <c r="Q110" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R110" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S110" s="6" t="inlineStr">
@@ -13280,25 +12150,15 @@
       </c>
       <c r="U110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V110" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W110" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X110" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y110" s="5" t="inlineStr"/>
+      <c r="W110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -13367,12 +12227,12 @@
       </c>
       <c r="Q111" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R111" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S111" s="6" t="inlineStr">
@@ -13387,25 +12247,15 @@
       </c>
       <c r="U111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V111" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W111" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X111" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y111" s="5" t="inlineStr"/>
+      <c r="W111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -13474,12 +12324,12 @@
       </c>
       <c r="Q112" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="R112" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="S112" s="6" t="inlineStr">
@@ -13494,30 +12344,20 @@
       </c>
       <c r="U112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>Huella dactilar</t>
         </is>
       </c>
       <c r="V112" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="W112" s="6" t="inlineStr">
-        <is>
-          <t>Huella dactilar</t>
-        </is>
-      </c>
-      <c r="X112" s="6" t="inlineStr">
-        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Y112" s="5" t="inlineStr"/>
+      <c r="W112" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reporte_Asistencia_Procesado_Nuevo.xlsx
+++ b/Reporte_Asistencia_Procesado_Nuevo.xlsx
@@ -709,22 +709,22 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
@@ -826,22 +826,22 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
@@ -1052,22 +1052,22 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
@@ -1282,22 +1282,22 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -1395,22 +1395,22 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
@@ -1629,22 +1629,22 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -2073,22 +2073,22 @@
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
@@ -2190,22 +2190,22 @@
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
@@ -2303,22 +2303,22 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
@@ -2529,22 +2529,22 @@
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -2642,22 +2642,22 @@
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
@@ -2872,22 +2872,22 @@
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
@@ -2989,22 +2989,22 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
@@ -3102,22 +3102,22 @@
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
@@ -3562,22 +3562,22 @@
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
@@ -3796,22 +3796,22 @@
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
@@ -4236,22 +4236,22 @@
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
@@ -4349,22 +4349,22 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
@@ -4692,22 +4692,22 @@
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
@@ -4914,22 +4914,22 @@
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
@@ -6153,22 +6153,22 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
@@ -6266,22 +6266,22 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
@@ -6492,22 +6492,22 @@
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
@@ -6605,22 +6605,22 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
@@ -6948,22 +6948,22 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
@@ -7065,22 +7065,22 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
@@ -7182,22 +7182,22 @@
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
@@ -7299,22 +7299,22 @@
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
@@ -7412,22 +7412,22 @@
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
@@ -7763,22 +7763,22 @@
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
@@ -7876,22 +7876,22 @@
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
@@ -7993,22 +7993,22 @@
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
@@ -8106,22 +8106,22 @@
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q78" s="6" t="inlineStr">
